--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488047_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488047_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E. LALI VICENTE UCHUATE</t>
+          <t>P. BILEISIS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9824000000000001</v>
+        <v>1.8553</v>
       </c>
       <c r="E2" t="n">
-        <v>2.052</v>
+        <v>1.4522</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0696</v>
+        <v>0.4031</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5105</v>
+        <v>-1.6479</v>
       </c>
       <c r="H2" t="n">
-        <v>2.0921</v>
+        <v>-0.0867</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5817</v>
+        <v>-1.5612</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4284</v>
+        <v>-0.7531</v>
       </c>
       <c r="K2" t="n">
-        <v>2.3481</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0804</v>
+        <v>-1.3181</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.918</v>
+        <v>-0.8948</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.256</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.662</v>
+        <v>-0.2431</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9911</v>
+        <v>1.784</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R2" t="n">
-        <v>1.9822</v>
+        <v>2.7751</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8951</v>
+        <v>-1.2985</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2886</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3936</v>
+        <v>-1.2106</v>
       </c>
       <c r="V2" t="n">
-        <v>-2.4142</v>
+        <v>3.0178</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.674</v>
+        <v>3.2843</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.7403</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. PEÑA BAÑOS</t>
+          <t>E. LALI VICENTE UCHUATE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3027</v>
+        <v>0.5564</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3027</v>
+        <v>1.4013</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0.8449</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3027</v>
+        <v>1.5105</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3027</v>
+        <v>2.0921</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0.5817</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3027</v>
+        <v>2.4284</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3027</v>
+        <v>2.3481</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.0804</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-0.918</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-0.256</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-0.662</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.9822</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.469</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.6379</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0.1689</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-2.4142</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.7403</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. BILEISIS</t>
+          <t>V. STRUKOV STRUKOV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2616</v>
+        <v>0.5082</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1674</v>
+        <v>0.4636</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.0446</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.6479</v>
+        <v>1.5358</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0867</v>
+        <v>0.8164</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.5612</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.7531</v>
+        <v>1.5939</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.5537</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.3181</v>
+        <v>0.0402</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8948</v>
+        <v>-0.0581</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6516999999999999</v>
+        <v>-0.7372</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2431</v>
+        <v>0.6791</v>
       </c>
       <c r="P4" t="n">
-        <v>1.784</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7751</v>
+        <v>0.5947</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.8922</v>
+        <v>-0.5607</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3727</v>
+        <v>-0.0688</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.5195</v>
+        <v>-0.4919</v>
       </c>
       <c r="V4" t="n">
-        <v>3.0178</v>
+        <v>-0.0704</v>
       </c>
       <c r="W4" t="n">
-        <v>3.2843</v>
+        <v>-0.0704</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. STRUKOV STRUKOV</t>
+          <t>N. PEÑA BAÑOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.3027</v>
       </c>
       <c r="E5" t="n">
-        <v>0.158</v>
+        <v>0.3027</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0677</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5358</v>
+        <v>0.3027</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8164</v>
+        <v>0.3027</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7193000000000001</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5939</v>
+        <v>0.3027</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5537</v>
+        <v>0.3027</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0402</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0581</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7372</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6791</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3964</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9786</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3744</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6042999999999999</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0704</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.0704</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -922,10 +922,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.07829999999999999</v>
+        <v>0.0089</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4442</v>
+        <v>-0.0762</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3659</v>
+        <v>0.0851</v>
       </c>
       <c r="G7" t="n">
         <v>-1.7946</v>
@@ -1000,13 +1000,13 @@
         <v>2.5769</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9508</v>
+        <v>-0.8636</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3816</v>
+        <v>-0.0136</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5692</v>
+        <v>-0.8499</v>
       </c>
       <c r="V7" t="n">
         <v>1.0813</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9441000000000001</v>
+        <v>-0.8037</v>
       </c>
       <c r="E8" t="n">
         <v>-0.1543</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7897999999999999</v>
+        <v>-0.6494</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3959</v>
@@ -1078,13 +1078,13 @@
         <v>0.9911</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3322</v>
+        <v>-0.1918</v>
       </c>
       <c r="T8" t="n">
         <v>0.1176</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4497</v>
+        <v>-0.3093</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2071</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2695</v>
+        <v>-1.1676</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="F9" t="n">
         <v>-1.2071</v>
@@ -1156,10 +1156,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1982</v>
+        <v>-0.0964</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="U9" t="n">
         <v>-0.1358</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. CONTRERAS RUBINO</t>
+          <t>J. REVUELTAS PAREJA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0497</v>
+        <v>-1.5674</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7028</v>
+        <v>-2.094</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6531</v>
+        <v>0.5266</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.449</v>
+        <v>-0.9943</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.4912</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.885</v>
+        <v>-0.5031</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.4747</v>
+        <v>-1.2777</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1614</v>
+        <v>0.0404</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.6362</v>
+        <v>-1.3181</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9743000000000001</v>
+        <v>0.2834</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7255</v>
+        <v>-0.5315</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2488</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9911</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9822</v>
+        <v>0.5947</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1953</v>
+        <v>-0.4432</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.444</v>
+        <v>-0.0917</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2487</v>
+        <v>-0.3515</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6036</v>
+        <v>0.2666</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2071</v>
+        <v>0.2666</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. REVUELTAS PAREJA</t>
+          <t>A. CONTRERAS RUBINO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1714</v>
+        <v>-1.7754</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5014</v>
+        <v>-2.0916</v>
       </c>
       <c r="F11" t="n">
-        <v>0.33</v>
+        <v>0.3161</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9943</v>
+        <v>-3.449</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4912</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5031</v>
+        <v>-2.885</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2777</v>
+        <v>-2.4747</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0404</v>
+        <v>0.1614</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3181</v>
+        <v>-2.6362</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2834</v>
+        <v>-0.9743000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5315</v>
+        <v>-0.7255</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8149999999999999</v>
+        <v>-0.2488</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3964</v>
+        <v>0.9911</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5947</v>
+        <v>1.9822</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0473</v>
+        <v>0.0789</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4992</v>
+        <v>0.1672</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5481</v>
+        <v>-0.0883</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2666</v>
+        <v>0.6036</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2666</v>
+        <v>1.2071</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. PENA BANOS</t>
+          <t>D. RUBIO MIRAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5882</v>
+        <v>-3.2749</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4683</v>
+        <v>-1.7368</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.12</v>
+        <v>-1.538</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.3308</v>
+        <v>-3.3749</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.2466</v>
+        <v>-1.1998</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0842</v>
+        <v>-2.175</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.0863</v>
+        <v>-1.5991</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.4473</v>
+        <v>0.0611</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.639</v>
+        <v>-1.6602</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2446</v>
+        <v>-1.7757</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7993</v>
+        <v>-1.2609</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5547</v>
+        <v>-0.5148</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.3787</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q12" t="n">
         <v>-2.9733</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5947</v>
+        <v>2.5769</v>
       </c>
       <c r="S12" t="n">
-        <v>2.3215</v>
+        <v>-0.4441</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5845</v>
+        <v>0.4214</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.263</v>
+        <v>-0.8655</v>
       </c>
       <c r="V12" t="n">
-        <v>0.7997</v>
+        <v>0.9405</v>
       </c>
       <c r="W12" t="n">
-        <v>2.0068</v>
+        <v>2.4142</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2071</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. RUBIO MIRAS</t>
+          <t>N. PENA BANOS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.1159</v>
+        <v>-4.6922</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.4936</v>
+        <v>-3.4038</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6223</v>
+        <v>-1.2884</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.3749</v>
+        <v>-3.3308</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.1998</v>
+        <v>-3.2466</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.175</v>
+        <v>-0.0842</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.5991</v>
+        <v>-3.0863</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0611</v>
+        <v>-2.4473</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.6602</v>
+        <v>-0.639</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.7757</v>
+        <v>-0.2446</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2609</v>
+        <v>-0.7993</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5148</v>
+        <v>0.5547</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.3964</v>
+        <v>-2.3787</v>
       </c>
       <c r="Q13" t="n">
         <v>-2.9733</v>
       </c>
       <c r="R13" t="n">
-        <v>2.5769</v>
+        <v>0.5947</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2851</v>
+        <v>0.2175</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6647</v>
+        <v>0.649</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9498</v>
+        <v>-0.4314</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9405</v>
+        <v>0.7997</v>
       </c>
       <c r="W13" t="n">
-        <v>2.4142</v>
+        <v>2.0068</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.4737</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.0027</v>
+        <v>-7.323</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.3607</v>
+        <v>-5.4002</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.642</v>
+        <v>-1.9228</v>
       </c>
       <c r="G14" t="n">
         <v>-3.6716</v>
@@ -1546,13 +1546,13 @@
         <v>1.1893</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.07340000000000001</v>
+        <v>-0.3937</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0479</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1213</v>
+        <v>-0.4021</v>
       </c>
       <c r="V14" t="n">
         <v>-1.4737</v>
@@ -1579,19 +1579,19 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-17.6452</v>
+        <v>-17.3332</v>
       </c>
       <c r="E15" t="n">
-        <v>-11.57</v>
+        <v>-11.2581</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.075200000000001</v>
+        <v>-6.075100000000001</v>
       </c>
       <c r="G15" t="n">
         <v>-15.1742</v>
       </c>
       <c r="H15" t="n">
-        <v>-7.760999999999999</v>
+        <v>-7.761000000000001</v>
       </c>
       <c r="I15" t="n">
         <v>-7.4134</v>
@@ -1600,16 +1600,16 @@
         <v>-8.7217</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1925000000000017</v>
+        <v>0.1924999999999994</v>
       </c>
       <c r="L15" t="n">
-        <v>-8.914200000000001</v>
+        <v>-8.914199999999999</v>
       </c>
       <c r="M15" t="n">
         <v>-6.4527</v>
       </c>
       <c r="N15" t="n">
-        <v>-7.9535</v>
+        <v>-7.953500000000001</v>
       </c>
       <c r="O15" t="n">
         <v>1.5009</v>
@@ -1624,16 +1624,16 @@
         <v>15.8578</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.798899999999999</v>
+        <v>-3.487100000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>1.506599999999999</v>
+        <v>1.8185</v>
       </c>
       <c r="U15" t="n">
-        <v>-5.3056</v>
+        <v>-5.3052</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3369999999999997</v>
+        <v>0.3369999999999993</v>
       </c>
       <c r="W15" t="n">
         <v>10.5119</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>8.800700000000001</v>
+        <v>8.8079</v>
       </c>
       <c r="E16" t="n">
-        <v>5.7744</v>
+        <v>5.9782</v>
       </c>
       <c r="F16" t="n">
-        <v>3.0263</v>
+        <v>2.8298</v>
       </c>
       <c r="G16" t="n">
         <v>5.512</v>
@@ -1702,13 +1702,13 @@
         <v>2.1805</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5553</v>
+        <v>0.5625</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4223</v>
+        <v>0.626</v>
       </c>
       <c r="U16" t="n">
-        <v>0.133</v>
+        <v>-0.0635</v>
       </c>
       <c r="V16" t="n">
         <v>1.5441</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>7.1809</v>
+        <v>6.7597</v>
       </c>
       <c r="E17" t="n">
         <v>4.0776</v>
       </c>
       <c r="F17" t="n">
-        <v>3.1033</v>
+        <v>2.6821</v>
       </c>
       <c r="G17" t="n">
         <v>4.1185</v>
@@ -1780,13 +1780,13 @@
         <v>2.3787</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6242</v>
+        <v>1.203</v>
       </c>
       <c r="T17" t="n">
         <v>0.6095</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0147</v>
+        <v>0.5936</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9405</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>5.9652</v>
+        <v>5.431</v>
       </c>
       <c r="E18" t="n">
-        <v>4.4186</v>
+        <v>3.6037</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5466</v>
+        <v>1.8274</v>
       </c>
       <c r="G18" t="n">
         <v>2.8348</v>
@@ -1858,13 +1858,13 @@
         <v>2.1805</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4831</v>
+        <v>0.9489</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9678</v>
+        <v>1.1528</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4847</v>
+        <v>-0.2039</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5331</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.1048</v>
+        <v>3.4885</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3363</v>
+        <v>0.6824</v>
       </c>
       <c r="F19" t="n">
-        <v>2.441</v>
+        <v>2.8061</v>
       </c>
       <c r="G19" t="n">
         <v>2.2689</v>
@@ -1936,13 +1936,13 @@
         <v>1.5858</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.7499</v>
+        <v>-0.3662</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8112</v>
+        <v>0.2075</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9388</v>
+        <v>-0.5737</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. IBANEZ FIDALGO</t>
+          <t>J. MUNOZ MENDOZA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.521</v>
+        <v>0.6397</v>
       </c>
       <c r="E20" t="n">
-        <v>2.4457</v>
+        <v>0.1847</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9247</v>
+        <v>0.455</v>
       </c>
       <c r="G20" t="n">
-        <v>3.0966</v>
+        <v>0.1099</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1299</v>
+        <v>2.1358</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9666</v>
+        <v>-2.026</v>
       </c>
       <c r="J20" t="n">
-        <v>2.6445</v>
+        <v>0.2225</v>
       </c>
       <c r="K20" t="n">
-        <v>1.9174</v>
+        <v>2.2599</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7271</v>
+        <v>-2.0374</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4521</v>
+        <v>-0.1126</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7875</v>
+        <v>-0.1241</v>
       </c>
       <c r="O20" t="n">
-        <v>1.2395</v>
+        <v>0.0114</v>
       </c>
       <c r="P20" t="n">
-        <v>-4.5591</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q20" t="n">
-        <v>-6.9378</v>
+        <v>-0.9911</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3787</v>
+        <v>0.7929</v>
       </c>
       <c r="S20" t="n">
-        <v>1.8469</v>
+        <v>0.0541</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5845</v>
+        <v>0.3497</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7376</v>
+        <v>-0.2956</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1367</v>
+        <v>0.674</v>
       </c>
       <c r="W20" t="n">
-        <v>4.1545</v>
+        <v>0.6036</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.0178</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MUNOZ MENDOZA</t>
+          <t>P. IBANEZ FIDALGO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.3175</v>
+        <v>0.5056</v>
       </c>
       <c r="E21" t="n">
-        <v>0.694</v>
+        <v>1.1214</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6235000000000001</v>
+        <v>-0.6158</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1099</v>
+        <v>3.0966</v>
       </c>
       <c r="H21" t="n">
-        <v>2.1358</v>
+        <v>1.1299</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.026</v>
+        <v>1.9666</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2225</v>
+        <v>2.6445</v>
       </c>
       <c r="K21" t="n">
-        <v>2.2599</v>
+        <v>1.9174</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.0374</v>
+        <v>0.7271</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1126</v>
+        <v>0.4521</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1241</v>
+        <v>-0.7875</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0114</v>
+        <v>1.2395</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1982</v>
+        <v>-4.5591</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9911</v>
+        <v>-6.9378</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7929</v>
+        <v>2.3787</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7319</v>
+        <v>0.8314</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8591</v>
+        <v>1.2602</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1271</v>
+        <v>-0.4288</v>
       </c>
       <c r="V21" t="n">
-        <v>0.674</v>
+        <v>1.1367</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6036</v>
+        <v>4.1545</v>
       </c>
       <c r="X21" t="n">
-        <v>0.0704</v>
+        <v>-3.0178</v>
       </c>
     </row>
     <row r="22">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1899</v>
+        <v>0.0347</v>
       </c>
       <c r="E23" t="n">
         <v>-1.015</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8250999999999999</v>
+        <v>1.0497</v>
       </c>
       <c r="G23" t="n">
         <v>-0.231</v>
@@ -2248,13 +2248,13 @@
         <v>0.5947</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.287</v>
+        <v>-0.0624</v>
       </c>
       <c r="T23" t="n">
         <v>0.2423</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5294</v>
+        <v>-0.3047</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2666</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8735000000000001</v>
+        <v>-0.9923</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.7862</v>
+        <v>-3.175</v>
       </c>
       <c r="F24" t="n">
-        <v>2.9127</v>
+        <v>2.1827</v>
       </c>
       <c r="G24" t="n">
         <v>1.2176</v>
@@ -2326,13 +2326,13 @@
         <v>2.1805</v>
       </c>
       <c r="S24" t="n">
-        <v>1.0915</v>
+        <v>0.9727</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0696</v>
+        <v>0.5416</v>
       </c>
       <c r="U24" t="n">
-        <v>1.1611</v>
+        <v>0.4311</v>
       </c>
       <c r="V24" t="n">
         <v>-0.4074</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.2017</v>
+        <v>-3.4677</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.5575</v>
+        <v>-4.0482</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3558</v>
+        <v>0.5805</v>
       </c>
       <c r="G25" t="n">
         <v>-2.6298</v>
@@ -2404,13 +2404,13 @@
         <v>0.3964</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9772</v>
+        <v>-0.2432</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.312</v>
+        <v>0.1974</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6652</v>
+        <v>-0.4406</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.2825</v>
+        <v>-3.8646</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.9429</v>
+        <v>-1.6373</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.3396</v>
+        <v>-2.2273</v>
       </c>
       <c r="G26" t="n">
         <v>-1.4257</v>
@@ -2482,13 +2482,13 @@
         <v>0.1982</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5198</v>
+        <v>-0.1019</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1872</v>
+        <v>0.1184</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3326</v>
+        <v>-0.2203</v>
       </c>
       <c r="V26" t="n">
         <v>-1.5441</v>
@@ -2518,10 +2518,10 @@
         <v>17.6452</v>
       </c>
       <c r="E27" t="n">
-        <v>6.075099999999997</v>
+        <v>6.075200000000004</v>
       </c>
       <c r="F27" t="n">
-        <v>11.57</v>
+        <v>11.5702</v>
       </c>
       <c r="G27" t="n">
         <v>15.1745</v>
@@ -2560,13 +2560,13 @@
         <v>14.8669</v>
       </c>
       <c r="S27" t="n">
-        <v>3.799</v>
+        <v>3.7989</v>
       </c>
       <c r="T27" t="n">
-        <v>5.305499999999999</v>
+        <v>5.305400000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.5066</v>
+        <v>-1.5064</v>
       </c>
       <c r="V27" t="n">
         <v>-0.3368999999999998</v>
